--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486534_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486534_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8457</v>
+        <v>7.7794</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7746</v>
+        <v>4.9549</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0711</v>
+        <v>2.8245</v>
       </c>
       <c r="G2" t="n">
         <v>3.8179</v>
@@ -610,13 +610,13 @@
         <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3101</v>
+        <v>1.2438</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8051</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5049</v>
+        <v>0.2584</v>
       </c>
       <c r="V2" t="n">
         <v>0.7602</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9968</v>
+        <v>5.6781</v>
       </c>
       <c r="E3" t="n">
-        <v>8.6668</v>
+        <v>7.8412</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.67</v>
+        <v>-2.1631</v>
       </c>
       <c r="G3" t="n">
         <v>4.1023</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8293</v>
+        <v>1.5105</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9528</v>
+        <v>1.1272</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.3833</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3698</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8465</v>
+        <v>1.5112</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4688</v>
+        <v>0.1335</v>
       </c>
       <c r="F4" t="n">
         <v>1.3777</v>
@@ -766,10 +766,10 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5105</v>
+        <v>1.1753</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0791</v>
+        <v>0.7439</v>
       </c>
       <c r="U4" t="n">
         <v>0.4314</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>D. SARAIVA SEIXAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2184</v>
+        <v>0.5471</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0506</v>
+        <v>1.9958</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8322000000000001</v>
+        <v>-1.4487</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8794</v>
+        <v>-0.5412</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3406</v>
+        <v>1.9554</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.22</v>
+        <v>-2.4965</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5591</v>
+        <v>-0.2805</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1095</v>
+        <v>1.1132</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6686</v>
+        <v>-1.3937</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3204</v>
+        <v>-0.2607</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2311</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5514</v>
+        <v>-1.1029</v>
       </c>
       <c r="P5" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.209</v>
+        <v>0.718</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.274</v>
+        <v>0.7559</v>
       </c>
       <c r="U5" t="n">
-        <v>0.065</v>
+        <v>-0.0379</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. SARAIVA SEIXAS</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3199</v>
+        <v>0.1147</v>
       </c>
       <c r="E6" t="n">
-        <v>1.437</v>
+        <v>2.4273</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7569</v>
+        <v>-2.3126</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5412</v>
+        <v>2.1954</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9554</v>
+        <v>1.4447</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.4965</v>
+        <v>0.7507</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2805</v>
+        <v>3.755</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1132</v>
+        <v>0.5205</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3937</v>
+        <v>3.2345</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2607</v>
+        <v>-1.5596</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.9242</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1029</v>
+        <v>-2.4838</v>
       </c>
       <c r="P6" t="n">
-        <v>1.305</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.149</v>
+        <v>0.2668</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1971</v>
+        <v>0.4999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3461</v>
+        <v>-0.2331</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9347</v>
+        <v>-1.695</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5204</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4552</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0375</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.645</v>
+        <v>-0.9388</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6825</v>
+        <v>0.863</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1954</v>
+        <v>-0.8794</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4447</v>
+        <v>0.3406</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7507</v>
+        <v>-1.22</v>
       </c>
       <c r="J7" t="n">
-        <v>3.755</v>
+        <v>-0.5591</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5205</v>
+        <v>0.1095</v>
       </c>
       <c r="L7" t="n">
-        <v>3.2345</v>
+        <v>-0.6686</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5596</v>
+        <v>-0.3204</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9242</v>
+        <v>0.2311</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.4838</v>
+        <v>-0.5514</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8854</v>
+        <v>-0.0664</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2824</v>
+        <v>-0.1622</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.603</v>
+        <v>0.0958</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4013</v>
+        <v>-0.9552</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2639</v>
+        <v>0.0281</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1373</v>
+        <v>-0.9832</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3633</v>
@@ -1078,13 +1078,13 @@
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.0916</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3425</v>
+        <v>-0.0505</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1953</v>
+        <v>-0.0412</v>
       </c>
       <c r="V8" t="n">
         <v>0.9347</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.478</v>
+        <v>-1.3277</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0983</v>
+        <v>0.2369</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3797</v>
+        <v>-1.5646</v>
       </c>
       <c r="G9" t="n">
         <v>0.2686</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3769</v>
+        <v>-0.2265</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3425</v>
+        <v>-0.0072</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0344</v>
+        <v>-0.2193</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9347</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>C. JÜRGENS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2825</v>
+        <v>-3.2835</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0926</v>
+        <v>0.0427</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3751</v>
+        <v>-3.3262</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8613</v>
+        <v>-0.7669</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8639</v>
+        <v>0.2921</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7252</v>
+        <v>-1.059</v>
       </c>
       <c r="J10" t="n">
-        <v>1.103</v>
+        <v>1.5664</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0648</v>
+        <v>-0.1365</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0382</v>
+        <v>1.7029</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9643</v>
+        <v>-2.3333</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2009</v>
+        <v>0.4286</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7635</v>
+        <v>-2.7619</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.8276</v>
+        <v>-0.435</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9714</v>
+        <v>-0.3866</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6872</v>
+        <v>-0.4362</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2842</v>
+        <v>0.0496</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.695</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. JÜRGENS</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4877</v>
+        <v>-3.7092</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-1.18</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4186</v>
+        <v>-2.5292</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7669</v>
+        <v>-0.8613</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2921</v>
+        <v>0.8639</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.059</v>
+        <v>-1.7252</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5664</v>
+        <v>1.103</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1365</v>
+        <v>1.0648</v>
       </c>
       <c r="L11" t="n">
-        <v>1.7029</v>
+        <v>0.0382</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3333</v>
+        <v>-1.9643</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4286</v>
+        <v>-0.2009</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.7619</v>
+        <v>-1.7635</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.435</v>
+        <v>-2.8276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5909</v>
+        <v>0.5447</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.548</v>
+        <v>0.4146</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0429</v>
+        <v>0.1301</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.695</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.695</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.8169</v>
+        <v>-7.2898</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8028</v>
+        <v>-5.3991</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0141</v>
+        <v>-1.8908</v>
       </c>
       <c r="G12" t="n">
         <v>-1.76</v>
@@ -1390,13 +1390,13 @@
         <v>1.305</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9248</v>
+        <v>-0.3978</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.3497</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1714</v>
+        <v>-0.0481</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8695</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.353199999999999</v>
+        <v>-1.010700000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>9.8001</v>
+        <v>10.1425</v>
       </c>
       <c r="F13" t="n">
         <v>-11.1532</v>
       </c>
       <c r="G13" t="n">
-        <v>6.200100000000001</v>
+        <v>6.200099999999999</v>
       </c>
       <c r="H13" t="n">
         <v>14.1726</v>
       </c>
       <c r="I13" t="n">
-        <v>-7.9723</v>
+        <v>-7.972300000000001</v>
       </c>
       <c r="J13" t="n">
         <v>17.5923</v>
@@ -1468,13 +1468,13 @@
         <v>13.0502</v>
       </c>
       <c r="S13" t="n">
-        <v>3.947500000000001</v>
+        <v>4.2902</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1784</v>
+        <v>3.521100000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7688999999999998</v>
+        <v>0.7689999999999998</v>
       </c>
       <c r="V13" t="n">
         <v>-8.238300000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3819</v>
+        <v>2.9788</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2329</v>
+        <v>1.9334</v>
       </c>
       <c r="F14" t="n">
-        <v>0.149</v>
+        <v>1.0455</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1096</v>
+        <v>1.7189</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4897</v>
+        <v>-0.1673</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5993</v>
+        <v>1.8862</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8478</v>
+        <v>2.5247</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0611</v>
+        <v>-0.2309</v>
       </c>
       <c r="L14" t="n">
-        <v>3.7867</v>
+        <v>2.7556</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7381</v>
+        <v>-0.8057</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5508</v>
+        <v>0.0636</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1873</v>
+        <v>-0.8694</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6203</v>
+        <v>-0.4128</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5178</v>
+        <v>-0.3064</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1025</v>
+        <v>-0.1064</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7395</v>
+        <v>1.8902</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.8902</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7167</v>
+        <v>2.1603</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4863</v>
+        <v>2.2271</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2304</v>
+        <v>-0.0668</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7189</v>
+        <v>2.1096</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1673</v>
+        <v>-0.4897</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8862</v>
+        <v>2.5993</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5247</v>
+        <v>3.8478</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2309</v>
+        <v>0.0611</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7556</v>
+        <v>3.7867</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8057</v>
+        <v>-1.7381</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0636</v>
+        <v>-0.5508</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8694</v>
+        <v>-1.1873</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.3987</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.5119</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0786</v>
+        <v>-0.1133</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8902</v>
+        <v>0.7395</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8902</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5802</v>
+        <v>1.9964</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3395</v>
+        <v>2.7865</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7593</v>
+        <v>-0.7901</v>
       </c>
       <c r="G16" t="n">
         <v>0.1408</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7776</v>
+        <v>-0.3614</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.2944</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0362</v>
+        <v>-0.067</v>
       </c>
       <c r="V16" t="n">
         <v>2.4345</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5326</v>
+        <v>0.8178</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6025</v>
+        <v>1.826</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0698</v>
+        <v>-1.0082</v>
       </c>
       <c r="G17" t="n">
         <v>0.7775</v>
@@ -1780,13 +1780,13 @@
         <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4624</v>
+        <v>-0.1772</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2055</v>
+        <v>0.018</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2569</v>
+        <v>-0.1953</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ BARRIENTOS</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1289</v>
+        <v>0.4371</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7902</v>
+        <v>1.1518</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9191</v>
+        <v>-0.7148</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6942</v>
+        <v>-0.6296</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.8193</v>
+        <v>-1.4655</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1251</v>
+        <v>0.8359</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2336</v>
+        <v>1.3061</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1434</v>
+        <v>-0.5681</v>
       </c>
       <c r="L18" t="n">
-        <v>1.377</v>
+        <v>1.8742</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.9278</v>
+        <v>-1.9357</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6759</v>
+        <v>-0.8974</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2519</v>
+        <v>-1.0383</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>2.3926</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0872</v>
+        <v>-1.2155</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4266</v>
+        <v>-0.2391</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5138</v>
+        <v>-0.9764</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>2.0647</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>V. VUCETIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1834</v>
+        <v>-0.4014</v>
       </c>
       <c r="E19" t="n">
-        <v>0.593</v>
+        <v>3.3115</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7764</v>
+        <v>-3.7128</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6296</v>
+        <v>-1.484</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4655</v>
+        <v>-1.9709</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8359</v>
+        <v>0.4869</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3061</v>
+        <v>0.1162</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5681</v>
+        <v>-0.7086</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8742</v>
+        <v>0.8248</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9357</v>
+        <v>-1.6003</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8974</v>
+        <v>-1.2624</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0383</v>
+        <v>-0.3379</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3926</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8359</v>
+        <v>-0.5921</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.1947</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.038</v>
+        <v>-0.3975</v>
       </c>
       <c r="V19" t="n">
-        <v>2.0647</v>
+        <v>0.3698</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2599</v>
+        <v>3.3899</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1952</v>
+        <v>-3.0202</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. VUCETIC</t>
+          <t>M. RODRIGUEZ BARRIENTOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6056</v>
+        <v>-0.4527</v>
       </c>
       <c r="E20" t="n">
-        <v>3.1997</v>
+        <v>1.3432</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.8053</v>
+        <v>-1.7958</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.484</v>
+        <v>-2.6942</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9709</v>
+        <v>-2.8193</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4869</v>
+        <v>0.1251</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1162</v>
+        <v>0.2336</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7086</v>
+        <v>-1.1434</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8248</v>
+        <v>1.377</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6003</v>
+        <v>-2.9278</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2624</v>
+        <v>-1.6759</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3379</v>
+        <v>-1.2519</v>
       </c>
       <c r="P20" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7964</v>
+        <v>-0.411</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3064</v>
+        <v>-0.0204</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4899</v>
+        <v>-0.3906</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3698</v>
+        <v>1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>3.3899</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.0202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7972</v>
+        <v>-1.466</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4033</v>
+        <v>-0.1029</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2006</v>
+        <v>-1.3631</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3581</v>
+        <v>-1.5655</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7151</v>
+        <v>-0.9734</v>
       </c>
       <c r="I21" t="n">
-        <v>1.357</v>
+        <v>-0.5921</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5296999999999999</v>
+        <v>-0.1166</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.9948</v>
+        <v>0.073</v>
       </c>
       <c r="L21" t="n">
-        <v>2.5245</v>
+        <v>-0.1896</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8878</v>
+        <v>-1.4488</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2796</v>
+        <v>-1.0464</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1674</v>
+        <v>-0.4024</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8409</v>
+        <v>-0.6183</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8736</v>
+        <v>-0.1815</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0327</v>
+        <v>-0.4368</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.0202</v>
+        <v>-0.3698</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.0202</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2039</v>
+        <v>-1.5294</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3442</v>
+        <v>0.7328</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.548</v>
+        <v>-2.2622</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5655</v>
+        <v>-0.3581</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9734</v>
+        <v>-1.7151</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5921</v>
+        <v>1.357</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1166</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.073</v>
+        <v>-1.9948</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1896</v>
+        <v>2.5245</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4488</v>
+        <v>-0.8878</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0464</v>
+        <v>0.2796</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4024</v>
+        <v>-1.1674</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3562</v>
+        <v>0.1088</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2656</v>
+        <v>0.2031</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6218</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3698</v>
+        <v>-3.0202</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-3.0202</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7545</v>
+        <v>-1.5643</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1232</v>
+        <v>-1.0264</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3688</v>
+        <v>-0.538</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8331</v>
+        <v>-3.3825</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5176</v>
+        <v>-0.8517</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6845</v>
+        <v>-2.5308</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2333</v>
+        <v>-0.9989</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3222</v>
+        <v>0.2801</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5554</v>
+        <v>-1.2789</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0663</v>
+        <v>-2.3836</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1954</v>
+        <v>-1.1318</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1291</v>
+        <v>-1.2519</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R23" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1438</v>
+        <v>-0.9415</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1815</v>
+        <v>-0.3076</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3253</v>
+        <v>-0.6339</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1952</v>
+        <v>3.1947</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1952</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1848</v>
+        <v>-1.6234</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5852</v>
+        <v>-1.8997</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5996</v>
+        <v>0.2763</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3825</v>
+        <v>-0.8331</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8517</v>
+        <v>-1.5176</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.5308</v>
+        <v>0.6845</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9989</v>
+        <v>0.2333</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2801</v>
+        <v>-0.3222</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2789</v>
+        <v>0.5554</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.3836</v>
+        <v>-1.0663</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1318</v>
+        <v>-1.1954</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2519</v>
+        <v>0.1291</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.435</v>
+        <v>-0.87</v>
       </c>
       <c r="Q24" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.562</v>
+        <v>0.2749</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8663999999999999</v>
+        <v>0.0421</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6956</v>
+        <v>0.2328</v>
       </c>
       <c r="V24" t="n">
-        <v>3.1947</v>
+        <v>-0.1952</v>
       </c>
       <c r="W24" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.7395</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.3531</v>
+        <v>1.3532</v>
       </c>
       <c r="E25" t="n">
-        <v>12.2832</v>
+        <v>12.2833</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.9299</v>
+        <v>-10.93</v>
       </c>
       <c r="G25" t="n">
         <v>-6.200199999999999</v>
@@ -2392,10 +2392,10 @@
         <v>-9.643599999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.9488</v>
+        <v>-7.948799999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>3.2626</v>
+        <v>3.262600000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.0505</v>
@@ -2404,22 +2404,22 @@
         <v>16.313</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.9476</v>
+        <v>-3.9474</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7689999999999999</v>
+        <v>-0.769</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.1785</v>
+        <v>-3.1787</v>
       </c>
       <c r="V25" t="n">
-        <v>8.238199999999999</v>
+        <v>8.238200000000001</v>
       </c>
       <c r="W25" t="n">
         <v>14.7103</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.472200000000001</v>
+        <v>-6.472199999999999</v>
       </c>
     </row>
   </sheetData>
